--- a/Excel/new_jobs_2026-07-19.xlsx
+++ b/Excel/new_jobs_2026-07-19.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>New</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>is_US</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>score</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>TZ</t>
         </is>
       </c>
     </row>
@@ -557,19 +557,19 @@
           <t>Figma is growing our team of passionate creatives and builders on a mission to make design accessible to all. Figma’s platform helps teams bring ideas to life—whether you're brainstorming, creating a prototype, translating designs into code, or iterating with AI. From idea to product, Figma empowers teams to streamline workflows, move faster, and work together in real time from anywhere in the world. If you're excited to shape the future of design and collaboration, join us! We are looking for an experienced Data Engineer to partner with our Data Science and Data Infrastructure teams to own and scale our data pipelines. You’ll also work closely with stakeholders across business teams including sales, marketing, and finance to ensure that the data they need arrives promptly and reliably. You’ll play an integral role in building the metrics and self-serve reporting capabilities to unlock Figma’s next phase of growth. This is a great role for an individual who is passionate about working with data and data systems, and who love s solving problems. You’ll have a good sense for when it makes sense to build fast, scrappy solution s to unblock a key stakeholder vs. when to push back or bring in an outside service. The ideal candidate will be a great communicator who can help coordinate across multiple internal and external teams and take s pride in building end-to-end projects. This is a full time role that can be held from one of our US hubs or remotely in the United States. What you'll do at Figma : Own, build, and maintai n scalable data pipelines that connect various cloud data sources. Develop a deep understanding of Figma’s core data model s and optimize data pipelines for scale. Partner with the Data Science and Data Infrastructure teams to build new foundational data sets that are trusted, well understood, and enable self-service . Work with a wide range of cross-functional stakeholders to derive requirements and architect shared datasets; ability to document, simplify and explain complex problems to different types of audiences. Establish best practices for the development of specialized data sets for analytics and modeling. We'd love to hear from you if you have: 4 + years in a relevant field. Fluency with both SQL and Python. Familiarity with Snowflake, dbt, Dagster, and ETL/reverse ETL tools. Excellent judgment and creative problem solving skills. A self-starting mindset along with strong communication and collaboration skills. While not required, it’s an added plus if you also have: Knowledge in data modeling methodologies to design and build robust data architectures for insightful analytics. Experience with business systems such as Salesforce , Customer IO, Stripe, NetSuite is a big plus. At Figma, one of our values is Grow as you go. We believe in hiring smart, curious people who are excited to learn and develop their skills. If you’re excited about this role but your past experience doesn’t align perfectly with the points outlined in the job description, we encourage you to apply anyways. You may be just the right candidate for this or other roles. Pay Transparency Disclosure If based in Figma’s San Francisco or New York hub offices, this role has the annual base salary range stated below. Job level and actual compensation will be decided based on factors including, but not limited to, individual qualifications objectively assessed during the interview process (including skills and prior relevant experience, potential impact, and scope of role), market demands, and specific work location. The listed range is a guideline, and the range for this role may be modified. For roles that are available to be filled remotely, the pay range is localized according to employee work location by a factor of between 80% and 100% of range. Please discuss your specific work location with your recruiter for more information. Figma offers equity to employees, as well a competitive package of additional benefits, including health, dental &amp; vision, retirement with company contribution, parental leave &amp; reproductive or family planning support, mental health &amp; wellness benefits, generous PTO, company recharge days, a learning &amp; development stipend, a work from home stipend, and cell phone reimbursement. Figma also offers sales incentive pay for most sales roles and an annual bonus plan for eligible non-sales roles. Figma’s compensation and benefits are subject to change and may be modified in the future. Annual Base Salary Range: $140,000 — $348,000 USD At Figma we celebrate and support our differences. We know employing a team rich in diverse thoughts, experiences, and opinions allows our employees, our product and our community to flourish. Figma is an equal opportunity workplace - we are dedicated to equal employment opportunities regardless of race, color, ancestry, religion, sex, national origin, sexual orientation, age, citizenship, marital status, disability, gender identity/expression, veteran status , or any other characteristic protected by law. We also consider qualified applicants regardless of criminal histories, consistent with legal requirements. We will work to ensure individuals with disabilities are provided reasonable accommodation to apply for a role, participate in the interview process, perform essential job functions, and receive other benefits and privileges of employment. If you require accommodation, please reach out to accommodations-ext@figma.com . These modifications enable an individual with a disability to have an equal opportunity not only to get a job, but successfully perform their job tasks to the same extent as people without disabilities. Examples of accommodations include but are not limited to: Holding interviews in an accessible location Enabling closed captioning on video conferencing Ensuring all written communication be compatible with screen readers Changing the mode or format of interviews To ensure the integrity of our hiring process and facilitate a more personal connection, we require all candidates keep their cameras on during video interviews. Additionally, if hired you will be required to attend in person onboarding. By applying for this job, the candidate acknowledges and agrees that any personal data contained in their application or supporting materials will be processed in accordance with Figma's Candidate Privacy Notice .</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>10001100001</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ET</t>
-        </is>
+      <c r="O2" t="n">
+        <v>1100001100001</v>
       </c>
     </row>
     <row r="3">
@@ -624,19 +624,19 @@
           <t>Figma is growing our team of passionate creatives and builders on a mission to make design accessible to all. Figma’s platform helps teams bring ideas to life—whether you're brainstorming, creating a prototype, translating designs into code, or iterating with AI. From idea to product, Figma empowers teams to streamline workflows, move faster, and work together in real time from anywhere in the world. If you're excited to shape the future of design and collaboration, join us! We are looking for an experienced Data Scientist to join our growing data team. At Figma, Data Scientists are deeply embedded within cross-functional teams across the company—from Product to Finance, Marketing, and Platform. We are hiring across a number of roles in these areas. This is ideal for someone excited to own high-impact data projects, partner strategically with stakeholders, and shape the future of our products and business. The ideal candidate will bring strong analytical and technical skills, business intuition, and a collaborative mindset to guide decision-making and unlock growth opportunities. You’ll work on problems ranging from understanding user behavior to optimizing revenue strategies, improving internal tooling, and influencing product direction through experimentation and data modeling. This is a full-time role that can be held from one of our US hubs or remotely in the United States. What you’ll do at Figma: Collaborate across teams to define and measure key metrics, design experiments, and uncover insights that inform strategic decisions Build models and analytical frameworks to support product, marketing, platform, or finance initiatives Develop tools, datasets, and systems that enable others to work with data more efficiently and rigorously Own complex data projects end-to-end—from problem scoping to solution delivery Champion data quality, accessibility, and the democratization of data across the organization Partner with Product, Engineering, Design, Research, Sales, Marketing, or Finance to drive impact We'd love to hear from you if you have: 4+ years of experience in Analytics, Data Science, or a related field Fluency in SQL and proficiency in a scripting language like Python or R Experience with distributed data systems (e.g., Redshift, Snowflake, Presto, Hive, Spark) Strong foundation in statistical methods, experimentation, and/or forecasting A track record of working cross-functionally and communicating effectively with both technical and non-technical partners Experience supporting one or more of the following: Product, Marketing, Finance, or internal Platform/Tooling teams While it’s not required, it’s an added plus if you also have: A self-starter attitude and the ability to thrive in ambiguous and fast-paced environments At Figma, one of our values is Grow as you go. We believe in hiring smart, curious people who are excited to learn and develop their skills. If you’re excited about this role but your past experience doesn’t align perfectly with the points outlined in the job description, we encourage you to apply anyways. You may be just the right candidate for this or other roles. Pay Transparency Disclosure If based in Figma’s San Francisco or New York hub offices, this role has the annual base salary range stated below. Job level and actual compensation will be decided based on factors including, but not limited to, individual qualifications objectively assessed during the interview process (including skills and prior relevant experience, potential impact, and scope of role), market demands, and specific work location. The listed range is a guideline, and the range for this role may be modified. For roles that are available to be filled remotely, the pay range is localized according to employee work location by a factor of between 80% and 100% of range. Please discuss your specific work location with your recruiter for more information. Figma offers equity to employees, as well a competitive package of additional benefits, including health, dental &amp; vision, retirement with company contribution, parental leave &amp; reproductive or family planning support, mental health &amp; wellness benefits, generous PTO, company recharge days, a learning &amp; development stipend, a work from home stipend, and cell phone reimbursement. Figma also offers sales incentive pay for most sales roles and an annual bonus plan for eligible non-sales roles. Figma’s compensation and benefits are subject to change and may be modified in the future. Annual Base Salary Range: $140,000 — $348,000 USD At Figma we celebrate and support our differences. We know employing a team rich in diverse thoughts, experiences, and opinions allows our employees, our product and our community to flourish. Figma is an equal opportunity workplace - we are dedicated to equal employment opportunities regardless of race, color, ancestry, religion, sex, national origin, sexual orientation, age, citizenship, marital status, disability, gender identity/expression, veteran status , or any other characteristic protected by law. We also consider qualified applicants regardless of criminal histories, consistent with legal requirements. We will work to ensure individuals with disabilities are provided reasonable accommodation to apply for a role, participate in the interview process, perform essential job functions, and receive other benefits and privileges of employment. If you require accommodation, please reach out to accommodations-ext@figma.com . These modifications enable an individual with a disability to have an equal opportunity not only to get a job, but successfully perform their job tasks to the same extent as people without disabilities. Examples of accommodations include but are not limited to: Holding interviews in an accessible location Enabling closed captioning on video conferencing Ensuring all written communication be compatible with screen readers Changing the mode or format of interviews To ensure the integrity of our hiring process and facilitate a more personal connection, we require all candidates keep their cameras on during video interviews. Additionally, if hired you will be required to attend in person onboarding. By applying for this job, the candidate acknowledges and agrees that any personal data contained in their application or supporting materials will be processed in accordance with Figma's Candidate Privacy Notice .</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>10001001001.1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>ET</t>
-        </is>
+      <c r="O3" t="n">
+        <v>1100001001001.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,19 +691,19 @@
           <t>Figma is growing our team of passionate creatives and builders on a mission to make design accessible to all. Figma’s platform helps teams bring ideas to life—whether you're brainstorming, creating a prototype, translating designs into code, or iterating with AI. From idea to product, Figma empowers teams to streamline workflows, move faster, and work together in real time from anywhere in the world. If you're excited to shape the future of design and collaboration, join us! Figma is growing our Finance Data Science team at a pivotal moment in the company's evolution. As a public company, the accuracy, scalability, and sophistication of our financial data systems have never been more important. At the same time, Figma's business continues to evolve through new products, AI-powered offerings, acquisitions, and emerging revenue models. We're looking for a Finance Data Scientist to help build the data foundation that powers financial reporting, forecasting, strategic decision-making, and investor communications. In this role, you'll partner closely with Strategic Finance, Accounting, Investor Relations, Engineering, Product, and Data teams to ensure our financial metrics are accurate, actionable, and trusted across the business. This is a unique opportunity to work at the intersection of finance, analytics, data engineering, and business strategy—helping shape how Figma measures and communicates its performance as the company scales. The data and systems built by this team directly support executive decision-making, public company reporting, and Figma's long-term growth strategy. This is a full time role that can be held from one of our US hubs or remotely in the United States. What you'll do at Figma: Own and improve the data models that power Figma's financial reporting, including ARR, revenue, billings, collections, and other key business metrics Build scalable reporting systems, forecasts, and analytical frameworks that support Finance, Accounting, Investor Relations, and executive leadership Drive data accuracy and completeness across month-end, quarter-end, and year-end close processes alongside Strategic Finance and Accounting teams Collaborate with Engineering, Product, GTM Systems, and Financial Systems teams to ensure the completeness and accuracy of financial data Conduct deep-dive analyses that inform strategic decisions and uncover opportunities to improve business performance Define, measure, and operationalize key financial and operational metrics Design and implement durable data solutions that balance immediate stakeholder needs with long-term scalability Serve as a trusted thought partner to Finance leaders, helping guide reporting, forecasting, and decision-making across the business We'd love to hear from you if you have: 3+ years of experience in Data Science, Analytics, Finance, Financial Systems, Data Engineering, or a related field Advanced SQL skills and strong proficiency in Python or a similar programming language Experience supporting Finance, Accounting, Strategic Finance, FP&amp;A, Investor Relations, or other finance-focused stakeholders Demonstrated ability to translate complex data into clear, actionable business insights for non-technical stakeholders Experience working independently and driving projects from ambiguity to execution While it's not required, it's an added plus if you also have: Experience with SaaS, subscription-based, usage-based, or consumption-based business models Knowledge of accounting concepts and revenue recognition principles (ASC 606) Experience with modern analytics and data engineering tools such as DBT, Snowflake, Git, Spark, Presto, or similar technologies Experience supporting IPO readiness, public company reporting, SOX controls, audits, or other major corporate milestones Background in Strategic Finance, FP&amp;A, Accounting, Investment Banking, Consulting, or related fields At Figma, one of our values is Grow as you go. We believe in hiring smart, curious people who are excited to learn and develop their skills. If you’re excited about this role but your past experience doesn’t align perfectly with the points outlined in the job description, we encourage you to apply anyways. You may be just the right candidate for this or other roles. Pay Transparency Disclosure If based in Figma’s San Francisco or New York hub offices, this role has the annual base salary range stated below. Job level and actual compensation will be decided based on factors including, but not limited to, individual qualifications objectively assessed during the interview process (including skills and prior relevant experience, potential impact, and scope of role), market demands, and specific work location. The listed range is a guideline, and the range for this role may be modified. For roles that are available to be filled remotely, the pay range is localized according to employee work location by a factor of between 80% and 100% of range. Please discuss your specific work location with your recruiter for more information. Figma offers equity to employees, as well a competitive package of additional benefits, including health, dental &amp; vision, retirement with company contribution, parental leave &amp; reproductive or family planning support, mental health &amp; wellness benefits, generous PTO, company recharge days, a learning &amp; development stipend, a work from home stipend, and cell phone reimbursement. Figma also offers sales incentive pay for most sales roles and an annual bonus plan for eligible non-sales roles. Figma’s compensation and benefits are subject to change and may be modified in the future. Annual Base Salary Range: $140,000 — $348,000 USD At Figma we celebrate and support our differences. We know employing a team rich in diverse thoughts, experiences, and opinions allows our employees, our product and our community to flourish. Figma is an equal opportunity workplace - we are dedicated to equal employment opportunities regardless of race, color, ancestry, religion, sex, national origin, sexual orientation, age, citizenship, marital status, disability, gender identity/expression, veteran status , or any other characteristic protected by law. We also consider qualified applicants regardless of criminal histories, consistent with legal requirements. We will work to ensure individuals with disabilities are provided reasonable accommodation to apply for a role, participate in the interview process, perform essential job functions, and receive other benefits and privileges of employment. If you require accommodation, please reach out to accommodations-ext@figma.com . These modifications enable an individual with a disability to have an equal opportunity not only to get a job, but successfully perform their job tasks to the same extent as people without disabilities. Examples of accommodations include but are not limited to: Holding interviews in an accessible location Enabling closed captioning on video conferencing Ensuring all written communication be compatible with screen readers Changing the mode or format of interviews To ensure the integrity of our hiring process and facilitate a more personal connection, we require all candidates keep their cameras on during video interviews. Additionally, if hired you will be required to attend in person onboarding. By applying for this job, the candidate acknowledges and agrees that any personal data contained in their application or supporting materials will be processed in accordance with Figma's Candidate Privacy Notice .</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
-        <v>10001000001.1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>ET</t>
-        </is>
+      <c r="O4" t="n">
+        <v>1100001000001.1</v>
       </c>
     </row>
     <row r="5">
@@ -758,19 +758,19 @@
           <t>Figma is growing our team of passionate creatives and builders on a mission to make design accessible to all. Figma’s platform helps teams bring ideas to life—whether you're brainstorming, creating a prototype, translating designs into code, or iterating with AI. From idea to product, Figma empowers teams to streamline workflows, move faster, and work together in real time from anywhere in the world. If you're excited to shape the future of design and collaboration, join us! We're looking for a Marketing Data Scientist to join Figma's Data Science team and help drive how we measure, optimize, and scale our marketing investments across the customer journey. In this role, you'll work closely with Paid Marketing, Lifecycle Marketing, Demand Generation, and Growth teams to develop measurement frameworks, improve targeting and segmentation, evaluate marketing effectiveness, and uncover insights that drive business growth. This role sits at the intersection of analytics, experimentation, and strategy. You'll work with marketing leaders to answer some of Figma's most important growth questions, including how we acquire and engage customers efficiently, which marketing investments drive incremental business impact, and how we can improve the effectiveness of our marketing programs at scale. This is a unique opportunity to shape the future of marketing measurement at Figma. You'll help build best-in-class capabilities across attribution, incrementality, experimentation, forecasting, and marketing mix modeling, while partnering with stakeholders across Marketing, Finance, Product, and Research to influence high-impact decisions and accelerate growth. What you'll do at Figma: Develop and own end-to-end measurement frameworks and attribution models to evaluate the effectiveness of Figma's marketing investments across the full funnel, channels, and regions. Partner with stakeholders across Brand Marketing, Email, Lifecycle, Demand Gen and Research teams to define success metrics, uncover insights, and drive data-informed decision making. Develop and apply statistical and machine learning models to solve key marketing challenges, including audience targeting, creative effectiveness, customer engagement, and campaign performance measurement. Assess the incremental impact of marketing investments across channels to inform budget allocation and growth strategies. Build dashboards, reporting frameworks, and analytical tools that help stakeholders understand brand performance and business impact. Translate complex analyses into clear recommendations for marketing leaders and executive stakeholders. Drive foundational improvements in data quality, measurement infrastructure, and reporting capabilities across the marketing organization. Identify new opportunities to improve marketing effectiveness and influence strategic planning through data-driven insights. We'd love to hear from you if you have: 5+ years of experience in Data Science, Marketing Analytics, or a related analytical role, supporting Marketing teams and measuring large-scale investments. Strong foundation in statistics, experimentation, causal inference, and working with survey or qualitative research data. Advanced proficiency in SQL and experience using Python, R, or similar tools to conduct analysis and build scalable measurement solutions. Demonstrated ability to communicate complex analyses clearly to senior non-technical stakeholders, with a track record of influencing decisions in cross-functional environments. While it's not required, it's an added plus if you also have: Experience with marketing mix modeling (MMM), multi-touch attribution, or incrementality testing. Familiarity with data visualization tools such as Tableau, Looker, or similar. Pay Transparency Disclosure If based in Figma’s San Francisco or New York hub offices, this role has the annual base salary range stated below. Job level and actual compensation will be decided based on factors including, but not limited to, individual qualifications objectively assessed during the interview process (including skills and prior relevant experience, potential impact, and scope of role), market demands, and specific work location. The listed range is a guideline, and the range for this role may be modified. For roles that are available to be filled remotely, the pay range is localized according to employee work location by a factor of between 80% and 100% of range. Please discuss your specific work location with your recruiter for more information. Figma offers equity to employees, as well a competitive package of additional benefits, including health, dental &amp; vision, retirement with company contribution, parental leave &amp; reproductive or family planning support, mental health &amp; wellness benefits, generous PTO, company recharge days, a learning &amp; development stipend, a work from home stipend, and cell phone reimbursement. Figma also offers sales incentive pay for most sales roles and an annual bonus plan for eligible non-sales roles. Figma’s compensation and benefits are subject to change and may be modified in the future. Annual Base Salary Range: $140,000 — $348,000 USD At Figma we celebrate and support our differences. We know employing a team rich in diverse thoughts, experiences, and opinions allows our employees, our product and our community to flourish. Figma is an equal opportunity workplace - we are dedicated to equal employment opportunities regardless of race, color, ancestry, religion, sex, national origin, sexual orientation, age, citizenship, marital status, disability, gender identity/expression, veteran status , or any other characteristic protected by law. We also consider qualified applicants regardless of criminal histories, consistent with legal requirements. We will work to ensure individuals with disabilities are provided reasonable accommodation to apply for a role, participate in the interview process, perform essential job functions, and receive other benefits and privileges of employment. If you require accommodation, please reach out to accommodations-ext@figma.com . These modifications enable an individual with a disability to have an equal opportunity not only to get a job, but successfully perform their job tasks to the same extent as people without disabilities. Examples of accommodations include but are not limited to: Holding interviews in an accessible location Enabling closed captioning on video conferencing Ensuring all written communication be compatible with screen readers Changing the mode or format of interviews To ensure the integrity of our hiring process and facilitate a more personal connection, we require all candidates keep their cameras on during video interviews. Additionally, if hired you will be required to attend in person onboarding. By applying for this job, the candidate acknowledges and agrees that any personal data contained in their application or supporting materials will be processed in accordance with Figma's Candidate Privacy Notice .</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
-        <v>10001001001</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ET</t>
-        </is>
+      <c r="O5" t="n">
+        <v>1100001001001</v>
       </c>
     </row>
   </sheetData>
